--- a/examples/recipients/recipients_sample.xlsx
+++ b/examples/recipients/recipients_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>姓名</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>研究方向</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>张教授</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +461,11 @@
           <t>李老师</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>电解液</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,6 +476,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>王老师</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>催化</t>
         </is>
       </c>
     </row>
